--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753344963_individual_h_4.xlsx
@@ -658,7 +658,7 @@
         <v>0.008423898014371441</v>
       </c>
       <c r="C2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>19013698</v>
+        <v>4516074</v>
       </c>
       <c r="L2" t="n">
-        <v>11480887</v>
+        <v>2527902</v>
       </c>
       <c r="M2" t="n">
-        <v>2997908</v>
+        <v>616813</v>
       </c>
       <c r="N2" t="n">
-        <v>178565</v>
+        <v>27511</v>
       </c>
       <c r="O2" t="n">
-        <v>1761469</v>
+        <v>381072</v>
       </c>
       <c r="P2" t="n">
-        <v>691663</v>
+        <v>153385</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999860525131226</v>
+        <v>0.9999955892562866</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9358108639717102</v>
+        <v>0.8811860084533691</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8652874231338501</v>
+        <v>0.7653340101242065</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8270716071128845</v>
+        <v>0.6994288563728333</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6475142240524292</v>
+        <v>0.4020077884197235</v>
       </c>
       <c r="V2" t="n">
-        <v>0.867840588092804</v>
+        <v>0.7528538107872009</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9080088138580322</v>
+        <v>0.8286288380622864</v>
       </c>
       <c r="X2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25385520</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566585421562195</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911242663860321</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581098318099976</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624432802200317</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020154476165771</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.00201873763595948</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>19013698</v>
+        <v>4516074</v>
       </c>
       <c r="E3" t="n">
-        <v>1227340</v>
+        <v>533534</v>
       </c>
       <c r="F3" t="n">
-        <v>21929</v>
+        <v>7418</v>
       </c>
       <c r="G3" t="n">
-        <v>2356</v>
+        <v>859</v>
       </c>
       <c r="H3" t="n">
-        <v>704</v>
+        <v>350</v>
       </c>
       <c r="I3" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>40278126</v>
+        <v>10069592</v>
       </c>
       <c r="K3" t="n">
-        <v>44093726</v>
+        <v>10748819</v>
       </c>
       <c r="L3" t="n">
-        <v>50767149</v>
+        <v>12356361</v>
       </c>
       <c r="M3" t="n">
-        <v>61301732</v>
+        <v>15216412</v>
       </c>
       <c r="N3" t="n">
-        <v>65209634</v>
+        <v>16285704</v>
       </c>
       <c r="O3" t="n">
-        <v>63358608</v>
+        <v>15781317</v>
       </c>
       <c r="P3" t="n">
-        <v>64820735</v>
+        <v>16190932</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9382027983665466</v>
+        <v>0.8928117752075195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8757721781730652</v>
+        <v>0.7696374654769897</v>
       </c>
       <c r="T3" t="n">
-        <v>0.802556037902832</v>
+        <v>0.6600319147109985</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4999566078186035</v>
+        <v>0.3078222870826721</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8646748661994934</v>
+        <v>0.7478085160255432</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8945552706718445</v>
+        <v>0.7933186888694763</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19408012</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>796241</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34282</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27251</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40278480</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44518633</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51392586</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61398817</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>65186364</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63427333</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64837792</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576596021652222</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099968671798706</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576393723487854</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619647741317749</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016187191009521</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03188454573346271</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1233549</v>
+        <v>577476</v>
       </c>
       <c r="E4" t="n">
-        <v>11480887</v>
+        <v>2527902</v>
       </c>
       <c r="F4" t="n">
-        <v>365828</v>
+        <v>161560</v>
       </c>
       <c r="G4" t="n">
-        <v>9329</v>
+        <v>4949</v>
       </c>
       <c r="H4" t="n">
-        <v>18554</v>
+        <v>11774</v>
       </c>
       <c r="I4" t="n">
-        <v>1295</v>
+        <v>873</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>28</v>
       </c>
       <c r="K4" t="n">
-        <v>1304188</v>
+        <v>608921</v>
       </c>
       <c r="L4" t="n">
-        <v>1787406</v>
+        <v>775103</v>
       </c>
       <c r="M4" t="n">
-        <v>626818</v>
+        <v>265068</v>
       </c>
       <c r="N4" t="n">
-        <v>97205</v>
+        <v>40923</v>
       </c>
       <c r="O4" t="n">
-        <v>268246</v>
+        <v>125098</v>
       </c>
       <c r="P4" t="n">
-        <v>70073</v>
+        <v>31722</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999930262565613</v>
+        <v>0.9999977946281433</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9370052814483643</v>
+        <v>0.8869608044624329</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8704982995986938</v>
+        <v>0.7674797177314758</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8146294355392456</v>
+        <v>0.6791595220565796</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5642479062080383</v>
+        <v>0.3486664295196533</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8662548661231995</v>
+        <v>0.750322699546814</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9012318253517151</v>
+        <v>0.8105894327163696</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>820988</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11929554</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>332033</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>22018</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>879281</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1161969</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>529733</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120475</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199521</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571588635444641</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106193780899048</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578745126724243</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622039079666138</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018170833587646</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>43033</v>
+        <v>19415</v>
       </c>
       <c r="E5" t="n">
-        <v>498565</v>
+        <v>210216</v>
       </c>
       <c r="F5" t="n">
-        <v>2997908</v>
+        <v>616813</v>
       </c>
       <c r="G5" t="n">
-        <v>42906</v>
+        <v>17177</v>
       </c>
       <c r="H5" t="n">
-        <v>145314</v>
+        <v>66166</v>
       </c>
       <c r="I5" t="n">
-        <v>7721</v>
+        <v>4732</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1252388</v>
+        <v>542186</v>
       </c>
       <c r="L5" t="n">
-        <v>1628558</v>
+        <v>756634</v>
       </c>
       <c r="M5" t="n">
-        <v>737542</v>
+        <v>317707</v>
       </c>
       <c r="N5" t="n">
-        <v>178596</v>
+        <v>61862</v>
       </c>
       <c r="O5" t="n">
-        <v>275677</v>
+        <v>128513</v>
       </c>
       <c r="P5" t="n">
-        <v>81529</v>
+        <v>39961</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999946355819702</v>
+        <v>0.9999982714653015</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9610657691955566</v>
+        <v>0.9298789501190186</v>
       </c>
       <c r="S5" t="n">
-        <v>0.947978138923645</v>
+        <v>0.9066924452781677</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9792221188545227</v>
+        <v>0.9644995927810669</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9957998394966125</v>
+        <v>0.9937387108802795</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9917165637016296</v>
+        <v>0.9845510125160217</v>
       </c>
       <c r="W5" t="n">
-        <v>0.99769127368927</v>
+        <v>0.9956333637237549</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32176</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>340707</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3203669</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39817</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116549</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>858074</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1179891</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>531781</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120733</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200417</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735417366027832</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643356800079346</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838341474533081</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963266253471375</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939092993736267</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983839988708496</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>27467</v>
+        <v>11972</v>
       </c>
       <c r="E6" t="n">
-        <v>41979</v>
+        <v>18242</v>
       </c>
       <c r="F6" t="n">
-        <v>77844</v>
+        <v>19821</v>
       </c>
       <c r="G6" t="n">
-        <v>178565</v>
+        <v>27511</v>
       </c>
       <c r="H6" t="n">
-        <v>29006</v>
+        <v>10798</v>
       </c>
       <c r="I6" t="n">
-        <v>2270</v>
+        <v>1019</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25894</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21451</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43534</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>236428</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27930</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>18601</v>
+        <v>12538</v>
       </c>
       <c r="F7" t="n">
-        <v>157189</v>
+        <v>73771</v>
       </c>
       <c r="G7" t="n">
-        <v>40967</v>
+        <v>17100</v>
       </c>
       <c r="H7" t="n">
-        <v>1761469</v>
+        <v>381072</v>
       </c>
       <c r="I7" t="n">
-        <v>58731</v>
+        <v>25075</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3246</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118564</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30328</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836729</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>204</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="E8" t="n">
-        <v>921</v>
+        <v>573</v>
       </c>
       <c r="F8" t="n">
-        <v>4028</v>
+        <v>2498</v>
       </c>
       <c r="G8" t="n">
-        <v>1647</v>
+        <v>838</v>
       </c>
       <c r="H8" t="n">
-        <v>74668</v>
+        <v>36010</v>
       </c>
       <c r="I8" t="n">
-        <v>691663</v>
+        <v>153385</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
